--- a/verification_forms/027_volunteer_verification_form--verification_forms.xlsx
+++ b/verification_forms/027_volunteer_verification_form--verification_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -800,7 +800,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_other_other</t>
+          <t>volunteer_verification_form_languages_spoken_other_other_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages Languages</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_other</t>
+          <t>volunteer_verification_form_languages_spoken_languages_other_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages Other 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages Other Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -938,12 +938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages Languages 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages Languages 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages Languages 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages</t>
+          <t>volunteer_verification_form_languages_spoken_languages_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages</t>
+          <t>volunteer_verification_form_languages_spoken_languages_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages</t>
+          <t>volunteer_verification_form_languages_spoken_languages_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Volunteer Verification Form Languages Spoken Languages 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1231,29 +1231,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_date_of_birth_yy_choices</t>
+          <t>volunteer_verification_form_languages_spoken_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1265,29 +1265,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_choices</t>
+          <t>volunteer_verification_form_languages_spoken_other_other_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1299,63 +1299,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_other_other_choices</t>
+          <t>volunteer_verification_form_languages_spoken_other_other_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_other_other_choices</t>
+          <t>volunteer_verification_form_languages_spoken_other_other_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_other_other_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1367,29 +1367,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1401,63 +1401,63 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_other_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_other_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_other_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_other_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_other_other_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1469,231 +1469,214 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_other_other_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_4_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_languages_4_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_3_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_3_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_4_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>volunteer_verification_form_languages_spoken_languages_choices</t>
+          <t>volunteer_verification_form_languages_spoken_languages_4_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>volunteer_verification_form_languages_spoken_languages_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
